--- a/LQT/check_vail.xlsx
+++ b/LQT/check_vail.xlsx
@@ -492,7 +492,7 @@
     <t>51</t>
   </si>
   <si>
-    <t>Lỗi MA_BENH_CHINH sai</t>
+    <t>Lỗi mã thẻ</t>
   </si>
   <si>
     <t>DTsheet23</t>
@@ -1784,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1920,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
